--- a/preview/pr-11/CodeSystem-dem-rentenstatus.xlsx
+++ b/preview/pr-11/CodeSystem-dem-rentenstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T11:48:58+00:00</t>
+    <t>2026-08-24T14:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-11/CodeSystem-dem-rentenstatus.xlsx
+++ b/preview/pr-11/CodeSystem-dem-rentenstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T14:28:57+00:00</t>
+    <t>2026-09-01T21:19:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
